--- a/Team-Data/2011-12/4-26-2011-12.xlsx
+++ b/Team-Data/2011-12/4-26-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,52 +728,52 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F2" t="n">
         <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>0.606</v>
+        <v>0.6</v>
       </c>
       <c r="H2" t="n">
         <v>49</v>
       </c>
       <c r="I2" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J2" t="n">
         <v>81</v>
       </c>
       <c r="K2" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L2" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M2" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="N2" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="O2" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="P2" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="Q2" t="n">
         <v>0.74</v>
       </c>
       <c r="R2" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="T2" t="n">
         <v>41.2</v>
@@ -715,7 +782,7 @@
         <v>22.4</v>
       </c>
       <c r="V2" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="W2" t="n">
         <v>8.1</v>
@@ -724,37 +791,37 @@
         <v>4.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>96.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF2" t="n">
         <v>8</v>
       </c>
       <c r="AG2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH2" t="n">
         <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ2" t="n">
         <v>19</v>
@@ -772,10 +839,10 @@
         <v>5</v>
       </c>
       <c r="AO2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AQ2" t="n">
         <v>23</v>
@@ -784,7 +851,7 @@
         <v>28</v>
       </c>
       <c r="AS2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
@@ -802,7 +869,7 @@
         <v>23</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ2" t="n">
         <v>6</v>
@@ -814,7 +881,7 @@
         <v>17</v>
       </c>
       <c r="BC2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F3" t="n">
         <v>27</v>
       </c>
       <c r="G3" t="n">
-        <v>0.591</v>
+        <v>0.585</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
@@ -861,46 +928,46 @@
         <v>35.5</v>
       </c>
       <c r="J3" t="n">
-        <v>77.09999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L3" t="n">
         <v>5.5</v>
       </c>
       <c r="M3" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="N3" t="n">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="O3" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="P3" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="R3" t="n">
         <v>7.7</v>
       </c>
       <c r="S3" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T3" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="U3" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="V3" t="n">
         <v>14.8</v>
       </c>
       <c r="W3" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X3" t="n">
         <v>5.5</v>
@@ -909,19 +976,19 @@
         <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>91.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
         <v>10</v>
@@ -945,7 +1012,7 @@
         <v>5</v>
       </c>
       <c r="AL3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM3" t="n">
         <v>24</v>
@@ -954,13 +1021,13 @@
         <v>7</v>
       </c>
       <c r="AO3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR3" t="n">
         <v>30</v>
@@ -972,16 +1039,16 @@
         <v>30</v>
       </c>
       <c r="AU3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV3" t="n">
         <v>17</v>
       </c>
       <c r="AW3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AX3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E4" t="n">
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G4" t="n">
-        <v>0.106</v>
+        <v>0.108</v>
       </c>
       <c r="H4" t="n">
         <v>48.2</v>
@@ -1043,7 +1110,7 @@
         <v>33.2</v>
       </c>
       <c r="J4" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="K4" t="n">
         <v>0.414</v>
@@ -1055,16 +1122,16 @@
         <v>13.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.295</v>
+        <v>0.293</v>
       </c>
       <c r="O4" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P4" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.746</v>
+        <v>0.749</v>
       </c>
       <c r="R4" t="n">
         <v>10.3</v>
@@ -1085,13 +1152,13 @@
         <v>6</v>
       </c>
       <c r="X4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y4" t="n">
         <v>5.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA4" t="n">
         <v>20.3</v>
@@ -1100,10 +1167,10 @@
         <v>87</v>
       </c>
       <c r="AC4" t="n">
-        <v>-13.9</v>
+        <v>-13.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1139,13 +1206,13 @@
         <v>16</v>
       </c>
       <c r="AP4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS4" t="n">
         <v>28</v>
@@ -1157,7 +1224,7 @@
         <v>19</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AW4" t="n">
         <v>29</v>
@@ -1166,13 +1233,13 @@
         <v>8</v>
       </c>
       <c r="AY4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA4" t="n">
         <v>10</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>9</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -1207,43 +1274,43 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
         <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>0.758</v>
+        <v>0.754</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
       </c>
       <c r="I5" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J5" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0.452</v>
+        <v>0.45</v>
       </c>
       <c r="L5" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M5" t="n">
         <v>16.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="O5" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="P5" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="Q5" t="n">
         <v>0.722</v>
@@ -1252,16 +1319,16 @@
         <v>13.9</v>
       </c>
       <c r="S5" t="n">
-        <v>32.8</v>
+        <v>32.6</v>
       </c>
       <c r="T5" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
       <c r="U5" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="V5" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W5" t="n">
         <v>6.9</v>
@@ -1276,16 +1343,16 @@
         <v>17.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.3</v>
+        <v>96.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1300,13 +1367,13 @@
         <v>16</v>
       </c>
       <c r="AI5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AL5" t="n">
         <v>17</v>
@@ -1318,10 +1385,10 @@
         <v>4</v>
       </c>
       <c r="AO5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AQ5" t="n">
         <v>27</v>
@@ -1330,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
@@ -1339,7 +1406,7 @@
         <v>5</v>
       </c>
       <c r="AV5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AW5" t="n">
         <v>24</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -1389,61 +1456,61 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E6" t="n">
         <v>21</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>0.318</v>
+        <v>0.323</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
       </c>
       <c r="I6" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="J6" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.422</v>
+        <v>0.423</v>
       </c>
       <c r="L6" t="n">
         <v>6.7</v>
       </c>
       <c r="M6" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.346</v>
+        <v>0.348</v>
       </c>
       <c r="O6" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P6" t="n">
         <v>24.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.716</v>
+        <v>0.717</v>
       </c>
       <c r="R6" t="n">
         <v>12.7</v>
       </c>
       <c r="S6" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T6" t="n">
         <v>42.3</v>
       </c>
       <c r="U6" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="V6" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W6" t="n">
         <v>7.1</v>
@@ -1455,34 +1522,34 @@
         <v>6.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB6" t="n">
-        <v>93</v>
+        <v>93.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>-7.2</v>
+        <v>-6.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH6" t="n">
         <v>10</v>
       </c>
       <c r="AI6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ6" t="n">
         <v>18</v>
@@ -1491,13 +1558,13 @@
         <v>29</v>
       </c>
       <c r="AL6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM6" t="n">
         <v>16</v>
       </c>
       <c r="AN6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO6" t="n">
         <v>9</v>
@@ -1518,7 +1585,7 @@
         <v>14</v>
       </c>
       <c r="AU6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AV6" t="n">
         <v>26</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -1571,37 +1638,37 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E7" t="n">
         <v>36</v>
       </c>
       <c r="F7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G7" t="n">
-        <v>0.545</v>
+        <v>0.554</v>
       </c>
       <c r="H7" t="n">
         <v>48.7</v>
       </c>
       <c r="I7" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J7" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K7" t="n">
         <v>0.443</v>
       </c>
       <c r="L7" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M7" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0.339</v>
+        <v>0.34</v>
       </c>
       <c r="O7" t="n">
         <v>15.6</v>
@@ -1637,19 +1704,19 @@
         <v>4</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AA7" t="n">
         <v>18.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>95.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
         <v>13</v>
@@ -1670,7 +1737,7 @@
         <v>14</v>
       </c>
       <c r="AK7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL7" t="n">
         <v>7</v>
@@ -1679,31 +1746,31 @@
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP7" t="n">
         <v>26</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR7" t="n">
         <v>27</v>
       </c>
       <c r="AS7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AU7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
         <v>4</v>
@@ -1715,7 +1782,7 @@
         <v>1</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA7" t="n">
         <v>27</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -1753,43 +1820,43 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E8" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F8" t="n">
         <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>0.576</v>
+        <v>0.569</v>
       </c>
       <c r="H8" t="n">
         <v>48.6</v>
       </c>
       <c r="I8" t="n">
-        <v>39</v>
+        <v>38.7</v>
       </c>
       <c r="J8" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K8" t="n">
-        <v>0.476</v>
+        <v>0.473</v>
       </c>
       <c r="L8" t="n">
         <v>6.6</v>
       </c>
       <c r="M8" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N8" t="n">
-        <v>0.332</v>
+        <v>0.331</v>
       </c>
       <c r="O8" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="P8" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="Q8" t="n">
         <v>0.735</v>
@@ -1798,13 +1865,13 @@
         <v>11.2</v>
       </c>
       <c r="S8" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T8" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U8" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="V8" t="n">
         <v>15.4</v>
@@ -1819,19 +1886,19 @@
         <v>6.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.1</v>
+        <v>103.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1858,7 +1925,7 @@
         <v>16</v>
       </c>
       <c r="AM8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN8" t="n">
         <v>24</v>
@@ -1873,7 +1940,7 @@
         <v>25</v>
       </c>
       <c r="AR8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS8" t="n">
         <v>7</v>
@@ -1897,7 +1964,7 @@
         <v>30</v>
       </c>
       <c r="AZ8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1906,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="BC8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -1935,58 +2002,58 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
         <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>0.379</v>
+        <v>0.369</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="J9" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="M9" t="n">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="N9" t="n">
-        <v>0.346</v>
+        <v>0.343</v>
       </c>
       <c r="O9" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="P9" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="Q9" t="n">
         <v>0.752</v>
       </c>
       <c r="R9" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S9" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="T9" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="U9" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="V9" t="n">
         <v>15.7</v>
@@ -2001,19 +2068,19 @@
         <v>5.3</v>
       </c>
       <c r="Z9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AA9" t="n">
         <v>19.6</v>
       </c>
-      <c r="AA9" t="n">
-        <v>19.4</v>
-      </c>
       <c r="AB9" t="n">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>-4.8</v>
+        <v>-5.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>22</v>
@@ -2043,28 +2110,28 @@
         <v>26</v>
       </c>
       <c r="AN9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AO9" t="n">
         <v>14</v>
       </c>
       <c r="AP9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ9" t="n">
         <v>18</v>
       </c>
       <c r="AR9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT9" t="n">
         <v>27</v>
       </c>
       <c r="AU9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AV9" t="n">
         <v>28</v>
@@ -2079,7 +2146,7 @@
         <v>21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA9" t="n">
         <v>16</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -2117,43 +2184,43 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>0.348</v>
+        <v>0.354</v>
       </c>
       <c r="H10" t="n">
         <v>48.2</v>
       </c>
       <c r="I10" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J10" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="M10" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0.388</v>
+        <v>0.389</v>
       </c>
       <c r="O10" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="P10" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="Q10" t="n">
         <v>0.77</v>
@@ -2162,16 +2229,16 @@
         <v>9.699999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T10" t="n">
         <v>39.2</v>
       </c>
       <c r="U10" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V10" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W10" t="n">
         <v>8</v>
@@ -2183,19 +2250,19 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA10" t="n">
         <v>16.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>97.8</v>
+        <v>97.7</v>
       </c>
       <c r="AC10" t="n">
         <v>-3.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2216,7 +2283,7 @@
         <v>10</v>
       </c>
       <c r="AK10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL10" t="n">
         <v>3</v>
@@ -2240,7 +2307,7 @@
         <v>29</v>
       </c>
       <c r="AS10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT10" t="n">
         <v>28</v>
@@ -2270,7 +2337,7 @@
         <v>12</v>
       </c>
       <c r="BC10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -2299,55 +2366,55 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F11" t="n">
         <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>0.515</v>
+        <v>0.508</v>
       </c>
       <c r="H11" t="n">
         <v>48.7</v>
       </c>
       <c r="I11" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J11" t="n">
-        <v>84</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.449</v>
+        <v>0.451</v>
       </c>
       <c r="L11" t="n">
         <v>7.2</v>
       </c>
       <c r="M11" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="N11" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O11" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="P11" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="Q11" t="n">
         <v>0.782</v>
       </c>
       <c r="R11" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S11" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T11" t="n">
-        <v>42.2</v>
+        <v>42</v>
       </c>
       <c r="U11" t="n">
         <v>21.3</v>
@@ -2368,16 +2435,16 @@
         <v>20.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.09999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>17</v>
@@ -2392,25 +2459,25 @@
         <v>3</v>
       </c>
       <c r="AI11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ11" t="n">
         <v>3</v>
       </c>
       <c r="AK11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AN11" t="n">
         <v>10</v>
       </c>
-      <c r="AN11" t="n">
-        <v>9</v>
-      </c>
       <c r="AO11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP11" t="n">
         <v>28</v>
@@ -2422,19 +2489,19 @@
         <v>14</v>
       </c>
       <c r="AS11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU11" t="n">
         <v>12</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX11" t="n">
         <v>20</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2641,7 @@
         <v>8</v>
       </c>
       <c r="AI12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ12" t="n">
         <v>16</v>
@@ -2604,19 +2671,19 @@
         <v>6</v>
       </c>
       <c r="AS12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX12" t="n">
         <v>9</v>
@@ -2634,7 +2701,7 @@
         <v>13</v>
       </c>
       <c r="BC12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2811,7 @@
         <v>1</v>
       </c>
       <c r="AE13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF13" t="n">
         <v>8</v>
@@ -2753,7 +2820,7 @@
         <v>8</v>
       </c>
       <c r="AH13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AI13" t="n">
         <v>13</v>
@@ -2783,10 +2850,10 @@
         <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS13" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AT13" t="n">
         <v>22</v>
@@ -2804,7 +2871,7 @@
         <v>22</v>
       </c>
       <c r="AY13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ13" t="n">
         <v>25</v>
@@ -2816,7 +2883,7 @@
         <v>14</v>
       </c>
       <c r="BC13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E14" t="n">
         <v>41</v>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G14" t="n">
-        <v>0.621</v>
+        <v>0.631</v>
       </c>
       <c r="H14" t="n">
         <v>48.7</v>
       </c>
       <c r="I14" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J14" t="n">
-        <v>80.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>0.457</v>
@@ -2872,16 +2939,16 @@
         <v>5.5</v>
       </c>
       <c r="M14" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.326</v>
+        <v>0.324</v>
       </c>
       <c r="O14" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="P14" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="Q14" t="n">
         <v>0.756</v>
@@ -2890,13 +2957,13 @@
         <v>12.1</v>
       </c>
       <c r="S14" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="T14" t="n">
-        <v>46.2</v>
+        <v>46.3</v>
       </c>
       <c r="U14" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V14" t="n">
         <v>15.1</v>
@@ -2905,31 +2972,31 @@
         <v>5.9</v>
       </c>
       <c r="X14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z14" t="n">
         <v>16.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB14" t="n">
         <v>97.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
       </c>
       <c r="AF14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="n">
         <v>6</v>
@@ -2938,16 +3005,16 @@
         <v>3</v>
       </c>
       <c r="AI14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ14" t="n">
         <v>22</v>
       </c>
       <c r="AK14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL14" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AM14" t="n">
         <v>19</v>
@@ -2959,7 +3026,7 @@
         <v>8</v>
       </c>
       <c r="AP14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ14" t="n">
         <v>16</v>
@@ -2977,7 +3044,7 @@
         <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW14" t="n">
         <v>30</v>
@@ -2986,13 +3053,13 @@
         <v>11</v>
       </c>
       <c r="AY14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ14" t="n">
         <v>1</v>
       </c>
       <c r="BA14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB14" t="n">
         <v>15</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -3027,25 +3094,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E15" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F15" t="n">
         <v>25</v>
       </c>
       <c r="G15" t="n">
-        <v>0.621</v>
+        <v>0.615</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J15" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="K15" t="n">
         <v>0.447</v>
@@ -3057,7 +3124,7 @@
         <v>12.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0.326</v>
+        <v>0.329</v>
       </c>
       <c r="O15" t="n">
         <v>17.3</v>
@@ -3066,19 +3133,19 @@
         <v>22.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.759</v>
+        <v>0.758</v>
       </c>
       <c r="R15" t="n">
         <v>12.6</v>
       </c>
       <c r="S15" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T15" t="n">
         <v>42</v>
       </c>
       <c r="U15" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="V15" t="n">
         <v>14.5</v>
@@ -3093,37 +3160,37 @@
         <v>5.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="n">
         <v>19.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH15" t="n">
         <v>16</v>
       </c>
       <c r="AI15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AJ15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK15" t="n">
         <v>16</v>
@@ -3144,22 +3211,22 @@
         <v>13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR15" t="n">
         <v>5</v>
       </c>
       <c r="AS15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU15" t="n">
         <v>24</v>
       </c>
       <c r="AV15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW15" t="n">
         <v>1</v>
@@ -3174,7 +3241,7 @@
         <v>19</v>
       </c>
       <c r="BA15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB15" t="n">
         <v>20</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -3209,28 +3276,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E16" t="n">
         <v>46</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>0.697</v>
+        <v>0.708</v>
       </c>
       <c r="H16" t="n">
         <v>48.6</v>
       </c>
       <c r="I16" t="n">
-        <v>37.1</v>
+        <v>37.3</v>
       </c>
       <c r="J16" t="n">
-        <v>79</v>
+        <v>79.2</v>
       </c>
       <c r="K16" t="n">
-        <v>0.469</v>
+        <v>0.471</v>
       </c>
       <c r="L16" t="n">
         <v>5.6</v>
@@ -3239,7 +3306,7 @@
         <v>15.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0.359</v>
+        <v>0.362</v>
       </c>
       <c r="O16" t="n">
         <v>18.8</v>
@@ -3254,16 +3321,16 @@
         <v>10.4</v>
       </c>
       <c r="S16" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="T16" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
       <c r="U16" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V16" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W16" t="n">
         <v>8.9</v>
@@ -3272,28 +3339,28 @@
         <v>5.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA16" t="n">
         <v>20.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>98.5</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
       </c>
       <c r="AF16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG16" t="n">
         <v>4</v>
@@ -3302,7 +3369,7 @@
         <v>6</v>
       </c>
       <c r="AI16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ16" t="n">
         <v>26</v>
@@ -3317,31 +3384,31 @@
         <v>23</v>
       </c>
       <c r="AN16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO16" t="n">
         <v>6</v>
       </c>
       <c r="AP16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>8</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>7</v>
       </c>
       <c r="AR16" t="n">
         <v>24</v>
       </c>
       <c r="AS16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AT16" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AU16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV16" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AW16" t="n">
         <v>3</v>
@@ -3359,10 +3426,10 @@
         <v>8</v>
       </c>
       <c r="BB16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -3391,37 +3458,37 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E17" t="n">
         <v>31</v>
       </c>
       <c r="F17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G17" t="n">
-        <v>0.47</v>
+        <v>0.477</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
       </c>
       <c r="I17" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J17" t="n">
-        <v>85.59999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="K17" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L17" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M17" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="O17" t="n">
         <v>16.6</v>
@@ -3430,22 +3497,22 @@
         <v>21.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.774</v>
+        <v>0.777</v>
       </c>
       <c r="R17" t="n">
         <v>12.4</v>
       </c>
       <c r="S17" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T17" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U17" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.1</v>
+        <v>13.9</v>
       </c>
       <c r="W17" t="n">
         <v>8.300000000000001</v>
@@ -3457,19 +3524,19 @@
         <v>4.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA17" t="n">
         <v>19.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>99</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
@@ -3490,7 +3557,7 @@
         <v>2</v>
       </c>
       <c r="AK17" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AL17" t="n">
         <v>15</v>
@@ -3499,7 +3566,7 @@
         <v>17</v>
       </c>
       <c r="AN17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO17" t="n">
         <v>15</v>
@@ -3508,7 +3575,7 @@
         <v>19</v>
       </c>
       <c r="AQ17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR17" t="n">
         <v>7</v>
@@ -3517,13 +3584,13 @@
         <v>20</v>
       </c>
       <c r="AT17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AW17" t="n">
         <v>7</v>
@@ -3532,13 +3599,13 @@
         <v>15</v>
       </c>
       <c r="AY17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ17" t="n">
         <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB17" t="n">
         <v>5</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -3573,55 +3640,55 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E18" t="n">
         <v>26</v>
       </c>
       <c r="F18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G18" t="n">
-        <v>0.394</v>
+        <v>0.4</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J18" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="K18" t="n">
         <v>0.433</v>
       </c>
       <c r="L18" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M18" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="N18" t="n">
         <v>0.332</v>
       </c>
       <c r="O18" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="P18" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.771</v>
+        <v>0.772</v>
       </c>
       <c r="R18" t="n">
         <v>12.1</v>
       </c>
       <c r="S18" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T18" t="n">
-        <v>43.7</v>
+        <v>44</v>
       </c>
       <c r="U18" t="n">
         <v>19.5</v>
@@ -3648,10 +3715,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-2.2</v>
+        <v>-1.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
         <v>21</v>
@@ -3666,16 +3733,16 @@
         <v>16</v>
       </c>
       <c r="AI18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK18" t="n">
         <v>27</v>
       </c>
       <c r="AL18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM18" t="n">
         <v>6</v>
@@ -3687,25 +3754,25 @@
         <v>4</v>
       </c>
       <c r="AP18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AS18" t="n">
         <v>8</v>
       </c>
       <c r="AT18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW18" t="n">
         <v>26</v>
@@ -3714,7 +3781,7 @@
         <v>24</v>
       </c>
       <c r="AY18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ18" t="n">
         <v>7</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -3755,46 +3822,46 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E19" t="n">
         <v>22</v>
       </c>
       <c r="F19" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G19" t="n">
-        <v>0.333</v>
+        <v>0.338</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="J19" t="n">
         <v>80.59999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.425</v>
+        <v>0.427</v>
       </c>
       <c r="L19" t="n">
         <v>7.7</v>
       </c>
       <c r="M19" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="N19" t="n">
         <v>0.342</v>
       </c>
       <c r="O19" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P19" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.777</v>
+        <v>0.778</v>
       </c>
       <c r="R19" t="n">
         <v>11.9</v>
@@ -3803,7 +3870,7 @@
         <v>28.5</v>
       </c>
       <c r="T19" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="U19" t="n">
         <v>19.9</v>
@@ -3812,43 +3879,43 @@
         <v>15.1</v>
       </c>
       <c r="W19" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X19" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="n">
         <v>5</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>93.09999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>-6</v>
+        <v>-5.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH19" t="n">
         <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ19" t="n">
         <v>21</v>
@@ -3872,25 +3939,25 @@
         <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR19" t="n">
         <v>11</v>
       </c>
       <c r="AS19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT19" t="n">
         <v>26</v>
       </c>
       <c r="AU19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV19" t="n">
         <v>19</v>
       </c>
       <c r="AW19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX19" t="n">
         <v>30</v>
@@ -3902,13 +3969,13 @@
         <v>12</v>
       </c>
       <c r="BA19" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BB19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -3937,25 +4004,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E20" t="n">
         <v>21</v>
       </c>
       <c r="F20" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G20" t="n">
-        <v>0.318</v>
+        <v>0.323</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>34.8</v>
+        <v>35</v>
       </c>
       <c r="J20" t="n">
-        <v>77.3</v>
+        <v>77.5</v>
       </c>
       <c r="K20" t="n">
         <v>0.451</v>
@@ -3964,7 +4031,7 @@
         <v>3.9</v>
       </c>
       <c r="M20" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="N20" t="n">
         <v>0.333</v>
@@ -3973,22 +4040,22 @@
         <v>16</v>
       </c>
       <c r="P20" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.757</v>
+        <v>0.76</v>
       </c>
       <c r="R20" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S20" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="T20" t="n">
         <v>41.1</v>
       </c>
       <c r="U20" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V20" t="n">
         <v>15.5</v>
@@ -4003,28 +4070,28 @@
         <v>5.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA20" t="n">
         <v>18.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>89.59999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.8</v>
+        <v>-3.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH20" t="n">
         <v>16</v>
@@ -4036,7 +4103,7 @@
         <v>29</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
         <v>30</v>
@@ -4051,13 +4118,13 @@
         <v>20</v>
       </c>
       <c r="AP20" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AQ20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS20" t="n">
         <v>19</v>
@@ -4084,13 +4151,13 @@
         <v>21</v>
       </c>
       <c r="BA20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB20" t="n">
         <v>29</v>
       </c>
       <c r="BC20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -4119,46 +4186,46 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F21" t="n">
         <v>30</v>
       </c>
       <c r="G21" t="n">
-        <v>0.545</v>
+        <v>0.538</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J21" t="n">
         <v>80.8</v>
       </c>
       <c r="K21" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L21" t="n">
         <v>7.8</v>
       </c>
       <c r="M21" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0.336</v>
+        <v>0.335</v>
       </c>
       <c r="O21" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="P21" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.741</v>
+        <v>0.743</v>
       </c>
       <c r="R21" t="n">
         <v>11.3</v>
@@ -4167,46 +4234,46 @@
         <v>30.5</v>
       </c>
       <c r="T21" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U21" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V21" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="W21" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="X21" t="n">
         <v>4.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z21" t="n">
         <v>21.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB21" t="n">
         <v>97.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH21" t="n">
         <v>16</v>
@@ -4218,7 +4285,7 @@
         <v>20</v>
       </c>
       <c r="AK21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="n">
         <v>4</v>
@@ -4233,22 +4300,22 @@
         <v>7</v>
       </c>
       <c r="AP21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR21" t="n">
         <v>15</v>
       </c>
       <c r="AS21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU21" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AV21" t="n">
         <v>29</v>
@@ -4260,7 +4327,7 @@
         <v>27</v>
       </c>
       <c r="AY21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ21" t="n">
         <v>24</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4461,7 @@
         <v>8</v>
       </c>
       <c r="AI22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="n">
         <v>25</v>
@@ -4403,10 +4470,10 @@
         <v>3</v>
       </c>
       <c r="AL22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN22" t="n">
         <v>11</v>
@@ -4421,7 +4488,7 @@
         <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS22" t="n">
         <v>3</v>
@@ -4430,7 +4497,7 @@
         <v>6</v>
       </c>
       <c r="AU22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
@@ -4454,7 +4521,7 @@
         <v>3</v>
       </c>
       <c r="BC22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E23" t="n">
         <v>37</v>
       </c>
       <c r="F23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.569</v>
       </c>
       <c r="H23" t="n">
         <v>48.4</v>
@@ -4501,7 +4568,7 @@
         <v>34.5</v>
       </c>
       <c r="J23" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="K23" t="n">
         <v>0.441</v>
@@ -4510,31 +4577,31 @@
         <v>10.2</v>
       </c>
       <c r="M23" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.375</v>
+        <v>0.377</v>
       </c>
       <c r="O23" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="P23" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="Q23" t="n">
         <v>0.66</v>
       </c>
       <c r="R23" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S23" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="T23" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="U23" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V23" t="n">
         <v>14.9</v>
@@ -4543,7 +4610,7 @@
         <v>6.8</v>
       </c>
       <c r="X23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y23" t="n">
         <v>4.1</v>
@@ -4552,25 +4619,25 @@
         <v>17.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH23" t="n">
         <v>10</v>
@@ -4582,7 +4649,7 @@
         <v>27</v>
       </c>
       <c r="AK23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4606,13 +4673,13 @@
         <v>16</v>
       </c>
       <c r="AS23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT23" t="n">
         <v>12</v>
       </c>
-      <c r="AT23" t="n">
-        <v>13</v>
-      </c>
       <c r="AU23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AV23" t="n">
         <v>18</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E24" t="n">
         <v>35</v>
       </c>
       <c r="F24" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G24" t="n">
-        <v>0.53</v>
+        <v>0.538</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="J24" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="K24" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L24" t="n">
         <v>5.3</v>
@@ -4695,7 +4762,7 @@
         <v>14.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O24" t="n">
         <v>13.5</v>
@@ -4704,16 +4771,16 @@
         <v>18.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.742</v>
+        <v>0.741</v>
       </c>
       <c r="R24" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S24" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T24" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U24" t="n">
         <v>22</v>
@@ -4731,28 +4798,28 @@
         <v>4.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="AA24" t="n">
         <v>16.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>93.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH24" t="n">
         <v>23</v>
@@ -4782,7 +4849,7 @@
         <v>30</v>
       </c>
       <c r="AQ24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR24" t="n">
         <v>22</v>
@@ -4800,7 +4867,7 @@
         <v>1</v>
       </c>
       <c r="AW24" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AX24" t="n">
         <v>13</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4995,7 @@
         <v>1</v>
       </c>
       <c r="AE25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF25" t="n">
         <v>18</v>
@@ -4949,22 +5016,22 @@
         <v>6</v>
       </c>
       <c r="AL25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM25" t="n">
         <v>15</v>
       </c>
       <c r="AN25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO25" t="n">
         <v>19</v>
       </c>
       <c r="AP25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR25" t="n">
         <v>21</v>
@@ -4973,7 +5040,7 @@
         <v>16</v>
       </c>
       <c r="AT25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU25" t="n">
         <v>6</v>
@@ -4991,7 +5058,7 @@
         <v>4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA25" t="n">
         <v>15</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E26" t="n">
         <v>28</v>
       </c>
       <c r="F26" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G26" t="n">
-        <v>0.424</v>
+        <v>0.431</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5053,13 +5120,13 @@
         <v>0.443</v>
       </c>
       <c r="L26" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M26" t="n">
         <v>20.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.346</v>
+        <v>0.348</v>
       </c>
       <c r="O26" t="n">
         <v>17.2</v>
@@ -5071,7 +5138,7 @@
         <v>0.796</v>
       </c>
       <c r="R26" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S26" t="n">
         <v>29.5</v>
@@ -5092,7 +5159,7 @@
         <v>4.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z26" t="n">
         <v>19</v>
@@ -5107,7 +5174,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
         <v>20</v>
@@ -5128,7 +5195,7 @@
         <v>13</v>
       </c>
       <c r="AK26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AL26" t="n">
         <v>9</v>
@@ -5137,7 +5204,7 @@
         <v>8</v>
       </c>
       <c r="AN26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO26" t="n">
         <v>11</v>
@@ -5149,10 +5216,10 @@
         <v>2</v>
       </c>
       <c r="AR26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT26" t="n">
         <v>25</v>
@@ -5167,13 +5234,13 @@
         <v>11</v>
       </c>
       <c r="AX26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA26" t="n">
         <v>14</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -5211,43 +5278,43 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F27" t="n">
         <v>44</v>
       </c>
       <c r="G27" t="n">
-        <v>0.333</v>
+        <v>0.323</v>
       </c>
       <c r="H27" t="n">
         <v>48.2</v>
       </c>
       <c r="I27" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J27" t="n">
         <v>86.5</v>
       </c>
       <c r="K27" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L27" t="n">
         <v>6.2</v>
       </c>
       <c r="M27" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0.316</v>
+        <v>0.315</v>
       </c>
       <c r="O27" t="n">
         <v>17.1</v>
       </c>
       <c r="P27" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q27" t="n">
         <v>0.736</v>
@@ -5256,16 +5323,16 @@
         <v>13.4</v>
       </c>
       <c r="S27" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T27" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U27" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="V27" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W27" t="n">
         <v>8.5</v>
@@ -5274,37 +5341,37 @@
         <v>4.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.8</v>
+        <v>98.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>-5.7</v>
+        <v>-6</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH27" t="n">
         <v>23</v>
       </c>
       <c r="AI27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ27" t="n">
         <v>1</v>
@@ -5334,37 +5401,37 @@
         <v>2</v>
       </c>
       <c r="AS27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU27" t="n">
         <v>26</v>
       </c>
       <c r="AV27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW27" t="n">
         <v>5</v>
       </c>
       <c r="AX27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY27" t="n">
         <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA27" t="n">
         <v>12</v>
       </c>
       <c r="BB27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -5393,58 +5460,58 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E28" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.758</v>
+        <v>0.754</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="J28" t="n">
-        <v>82.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.478</v>
+        <v>0.479</v>
       </c>
       <c r="L28" t="n">
         <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.393</v>
+        <v>0.395</v>
       </c>
       <c r="O28" t="n">
         <v>16.2</v>
       </c>
       <c r="P28" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.748</v>
+        <v>0.747</v>
       </c>
       <c r="R28" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S28" t="n">
         <v>32.6</v>
       </c>
       <c r="T28" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="U28" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V28" t="n">
         <v>13.6</v>
@@ -5459,19 +5526,19 @@
         <v>5</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.7</v>
+        <v>103.6</v>
       </c>
       <c r="AC28" t="n">
         <v>7.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK28" t="n">
         <v>1</v>
@@ -5510,13 +5577,13 @@
         <v>17</v>
       </c>
       <c r="AQ28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT28" t="n">
         <v>9</v>
@@ -5531,7 +5598,7 @@
         <v>20</v>
       </c>
       <c r="AX28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY28" t="n">
         <v>16</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -5575,25 +5642,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F29" t="n">
         <v>43</v>
       </c>
       <c r="G29" t="n">
-        <v>0.348</v>
+        <v>0.338</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>34.4</v>
+        <v>34.3</v>
       </c>
       <c r="J29" t="n">
-        <v>78.09999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K29" t="n">
         <v>0.44</v>
@@ -5602,28 +5669,28 @@
         <v>5.5</v>
       </c>
       <c r="M29" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0.34</v>
+        <v>0.336</v>
       </c>
       <c r="O29" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P29" t="n">
         <v>21.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R29" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S29" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="T29" t="n">
-        <v>42</v>
+        <v>41.7</v>
       </c>
       <c r="U29" t="n">
         <v>20.9</v>
@@ -5641,55 +5708,55 @@
         <v>4.9</v>
       </c>
       <c r="Z29" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="AA29" t="n">
         <v>18.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>90.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.3</v>
+        <v>-3.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH29" t="n">
         <v>10</v>
       </c>
       <c r="AI29" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AJ29" t="n">
         <v>28</v>
       </c>
       <c r="AK29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL29" t="n">
         <v>21</v>
       </c>
       <c r="AM29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AN29" t="n">
         <v>20</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>19</v>
       </c>
       <c r="AO29" t="n">
         <v>17</v>
       </c>
       <c r="AP29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ29" t="n">
         <v>12</v>
@@ -5698,22 +5765,22 @@
         <v>23</v>
       </c>
       <c r="AS29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AT29" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW29" t="n">
         <v>28</v>
       </c>
       <c r="AX29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY29" t="n">
         <v>14</v>
@@ -5728,7 +5795,7 @@
         <v>28</v>
       </c>
       <c r="BC29" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -5757,43 +5824,43 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E30" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F30" t="n">
         <v>30</v>
       </c>
       <c r="G30" t="n">
-        <v>0.545</v>
+        <v>0.538</v>
       </c>
       <c r="H30" t="n">
         <v>49</v>
       </c>
       <c r="I30" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J30" t="n">
         <v>83.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L30" t="n">
         <v>4.1</v>
       </c>
       <c r="M30" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="N30" t="n">
         <v>0.323</v>
       </c>
       <c r="O30" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="P30" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="Q30" t="n">
         <v>0.754</v>
@@ -5805,16 +5872,16 @@
         <v>31.1</v>
       </c>
       <c r="T30" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="U30" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V30" t="n">
         <v>14.2</v>
       </c>
       <c r="W30" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X30" t="n">
         <v>5.8</v>
@@ -5823,7 +5890,7 @@
         <v>5.7</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA30" t="n">
         <v>20.7</v>
@@ -5835,16 +5902,16 @@
         <v>0.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH30" t="n">
         <v>1</v>
@@ -5856,7 +5923,7 @@
         <v>4</v>
       </c>
       <c r="AK30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL30" t="n">
         <v>28</v>
@@ -5871,7 +5938,7 @@
         <v>5</v>
       </c>
       <c r="AP30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ30" t="n">
         <v>17</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
@@ -5939,37 +6006,37 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F31" t="n">
         <v>46</v>
       </c>
       <c r="G31" t="n">
-        <v>0.303</v>
+        <v>0.292</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J31" t="n">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.441</v>
+        <v>0.439</v>
       </c>
       <c r="L31" t="n">
         <v>5.2</v>
       </c>
       <c r="M31" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.32</v>
+        <v>0.318</v>
       </c>
       <c r="O31" t="n">
         <v>15.3</v>
@@ -5978,28 +6045,28 @@
         <v>21</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.727</v>
+        <v>0.729</v>
       </c>
       <c r="R31" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S31" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T31" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U31" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="V31" t="n">
         <v>15.3</v>
       </c>
       <c r="W31" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X31" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Y31" t="n">
         <v>4.5</v>
@@ -6011,13 +6078,13 @@
         <v>18.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>93.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>-4.8</v>
+        <v>-5.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6038,7 +6105,7 @@
         <v>6</v>
       </c>
       <c r="AK31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6050,10 +6117,10 @@
         <v>28</v>
       </c>
       <c r="AO31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ31" t="n">
         <v>26</v>
@@ -6065,7 +6132,7 @@
         <v>21</v>
       </c>
       <c r="AT31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU31" t="n">
         <v>27</v>
@@ -6074,7 +6141,7 @@
         <v>24</v>
       </c>
       <c r="AW31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX31" t="n">
         <v>2</v>
@@ -6086,10 +6153,10 @@
         <v>26</v>
       </c>
       <c r="BA31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB31" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC31" t="n">
         <v>26</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-26-2011-12</t>
+          <t>2012-04-26</t>
         </is>
       </c>
     </row>
